--- a/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ_번호별_증빙대응표_20261012_v3.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ_번호별_증빙대응표_20261012_v3.xlsx
@@ -2106,7 +2106,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>미지정</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>미지정</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
